--- a/firmware/Номера корректоров.xlsx
+++ b/firmware/Номера корректоров.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fs\FileServer\Production\BD_Corrector\Инструкция по выпуску корректоров\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B757E7B-BF17-4B0B-A1A5-683B1519C7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E5F63D-2785-47CD-B6DD-5C0612BCA19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="360" windowWidth="24330" windowHeight="15240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Корректоры" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="234">
   <si>
     <t>И1</t>
   </si>
@@ -855,6 +855,21 @@
   </si>
   <si>
     <t>DN100;2,0-400 (1:200); слева направо; О; Ксж-3; ПАД(0,08-0,2);ПТГ(4-60);БТ3)</t>
+  </si>
+  <si>
+    <t>(И4;ГК;3м;ПАД(0,15-0,75)+УК;1,5м; ПТГ(4-60)+УК(1/4NPT-105);1,5м; ±0,27 ;Ксж-2; ППД(0-1,6)+УК1,5м;ПТТП (4-60)+УК(М14-80);1,5м) Выпуск 09.2026</t>
+  </si>
+  <si>
+    <t>.09.2026</t>
+  </si>
+  <si>
+    <t>DN50;0,5-65 (1:130); справа налево; О; Ксж-2; ПАД(0,15-0,75);ПТГ(4-60);ППД(0-1,6);ПТТП(4-60))</t>
+  </si>
+  <si>
+    <t>DN80;1,6-250 (1:160); слева направо; О; Ксж-2; ПАД(0,15-0,75);ПТГ(4-60);ППД(0-4);БТ1)</t>
+  </si>
+  <si>
+    <t>(И2;ГК;3м;ПАД(0,15-0,75)+УК;1,5м; ПТГ(4-60)+УК(1/4NPT-105); 1,5м; ±0,27%;Ксж-2;ППД(0-4)+УК;1,5м) Выпуск 09.2026</t>
   </si>
 </sst>
 </file>
@@ -1703,7 +1718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2205,6 +2220,9 @@
     <xf numFmtId="0" fontId="34" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2499,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
@@ -5201,7 +5219,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="30.75" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="31.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5"/>
       <c r="B105" s="6">
         <v>3002608004</v>
@@ -5229,33 +5247,139 @@
         <v>802</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="137"/>
-      <c r="H106" s="134"/>
-      <c r="I106" s="157"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B106" s="107"/>
+      <c r="C106" s="17">
+        <v>46266</v>
+      </c>
+      <c r="D106" s="18"/>
+      <c r="E106" s="18"/>
+      <c r="F106" s="62"/>
+      <c r="G106" s="19"/>
+      <c r="H106" s="141"/>
+      <c r="I106" s="154"/>
+      <c r="J106" s="32"/>
+      <c r="K106" s="32"/>
+      <c r="L106" s="108"/>
+    </row>
+    <row r="107" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="137"/>
-      <c r="H107" s="134"/>
-      <c r="I107" s="157"/>
-      <c r="J107" s="5"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="5"/>
+      <c r="B107" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C107" s="102" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="E107" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="F107" s="104" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="105" t="s">
+        <v>12</v>
+      </c>
+      <c r="H107" s="142"/>
+      <c r="I107" s="152" t="s">
+        <v>73</v>
+      </c>
+      <c r="J107" s="66" t="s">
+        <v>74</v>
+      </c>
+      <c r="K107" s="66" t="s">
+        <v>75</v>
+      </c>
+      <c r="L107" s="106" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="6">
+        <v>3002609001</v>
+      </c>
+      <c r="F108" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="G108" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="H108" s="205" t="s">
+        <v>179</v>
+      </c>
+      <c r="I108" s="122" t="s">
+        <v>160</v>
+      </c>
+      <c r="J108" s="123" t="s">
+        <v>97</v>
+      </c>
+      <c r="K108" s="5"/>
+      <c r="L108" s="130">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="12">
+        <v>3002609002</v>
+      </c>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="G109" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="H109" s="197" t="s">
+        <v>193</v>
+      </c>
+      <c r="I109" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="J109" s="160" t="s">
+        <v>97</v>
+      </c>
+      <c r="K109" s="5"/>
+      <c r="L109" s="130">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="137"/>
+      <c r="H110" s="134"/>
+      <c r="I110" s="157"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="137"/>
+      <c r="H111" s="134"/>
+      <c r="I111" s="157"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -8188,60 +8312,136 @@
       </c>
       <c r="Q64" s="5"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="63" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C65" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="H65" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="I65" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="J65" s="126" t="s">
+        <v>78</v>
+      </c>
+      <c r="K65" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="L65" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="M65" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="N65" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="O65" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="P65" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q65" s="86" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
+      <c r="C66" s="93">
+        <v>3002609001</v>
+      </c>
+      <c r="D66" s="93">
+        <v>4002609001</v>
+      </c>
+      <c r="E66" s="93" t="s">
+        <v>181</v>
+      </c>
+      <c r="F66" s="93" t="s">
+        <v>231</v>
+      </c>
+      <c r="G66" s="93" t="s">
+        <v>160</v>
+      </c>
+      <c r="H66" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="I66" s="93" t="s">
+        <v>179</v>
+      </c>
+      <c r="J66" s="93">
+        <v>895</v>
+      </c>
+      <c r="K66" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="L66" s="93" t="s">
+        <v>198</v>
+      </c>
+      <c r="M66" s="98"/>
+      <c r="N66" s="87"/>
+      <c r="O66" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="P66" s="88"/>
       <c r="Q66" s="5"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
+      <c r="C67" s="93">
+        <v>3002609002</v>
+      </c>
+      <c r="D67" s="93">
+        <v>4002609002</v>
+      </c>
+      <c r="E67" s="93" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67" s="93" t="s">
+        <v>232</v>
+      </c>
+      <c r="G67" s="93" t="s">
+        <v>160</v>
+      </c>
+      <c r="H67" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="I67" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="J67" s="93">
+        <v>893</v>
+      </c>
+      <c r="K67" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="L67" s="93" t="s">
+        <v>180</v>
+      </c>
+      <c r="M67" s="98"/>
+      <c r="N67" s="87" t="s">
+        <v>104</v>
+      </c>
+      <c r="O67" s="93" t="s">
+        <v>88</v>
+      </c>
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
     </row>
